--- a/efa_results.xlsx
+++ b/efa_results.xlsx
@@ -494,28 +494,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0698</v>
+        <v>0.023</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0645</v>
+        <v>0.0177</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0435</v>
+        <v>0.0441</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0155</v>
+        <v>0.0154</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0362</v>
+        <v>-0.0658</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6445</v>
+        <v>0.6766</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1047</v>
+        <v>0.0968</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4388</v>
+        <v>0.4745</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.6445</v>
+        <v>0.6766</v>
       </c>
     </row>
     <row r="3">
@@ -538,28 +538,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0209</v>
+        <v>0.0254</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1185</v>
+        <v>0.1455</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0809</v>
+        <v>-0.0449</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1198</v>
+        <v>0.0568</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0285</v>
+        <v>-0.0316</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5487</v>
+        <v>0.5477</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0407</v>
+        <v>0.0578</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3389</v>
+        <v>0.3314</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.5487</v>
+        <v>0.5477</v>
       </c>
     </row>
     <row r="4">
@@ -582,28 +582,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0147</v>
+        <v>-0.0033</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0769</v>
+        <v>-0.0312</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0182</v>
+        <v>-0.0067</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0408</v>
+        <v>-0.0617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0723</v>
+        <v>0.0814</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7408</v>
+        <v>0.7457</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0041</v>
+        <v>-0.0054</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5622</v>
+        <v>0.5676</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.7408</v>
+        <v>0.7457</v>
       </c>
     </row>
     <row r="5">
@@ -626,28 +626,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0482</v>
+        <v>-0.0028</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0503</v>
+        <v>0.0158</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0091</v>
+        <v>0.0684</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0069</v>
+        <v>-0.0078</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6156</v>
+        <v>0.6482</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0442</v>
+        <v>-0.0456</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3946</v>
+        <v>0.4335</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.6156</v>
+        <v>0.6482</v>
       </c>
     </row>
     <row r="6">
@@ -670,28 +670,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0102</v>
+        <v>0.0507</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0212</v>
+        <v>0.045</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0851</v>
+        <v>0.0866</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0465</v>
+        <v>-0.0214</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1154</v>
+        <v>0.0917</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5482</v>
+        <v>0.5574</v>
       </c>
       <c r="H6" t="n">
-        <v>0.013</v>
+        <v>0.0281</v>
       </c>
       <c r="I6" t="n">
-        <v>0.324</v>
+        <v>0.3324</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.5482</v>
+        <v>0.5574</v>
       </c>
     </row>
     <row r="7">
@@ -714,28 +714,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7658</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0346</v>
+        <v>0.1087</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0515</v>
+        <v>0.0261</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1218</v>
+        <v>0.0387</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0679</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0555</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0289</v>
+        <v>-0.038</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6178</v>
+        <v>0.6653</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.7658</v>
+        <v>0.7989000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -758,28 +758,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7006</v>
+        <v>0.7527</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0419</v>
+        <v>-0.1523</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0264</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1341</v>
+        <v>0.0258</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1589</v>
+        <v>0.1443</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1289</v>
+        <v>0.1358</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0278</v>
+        <v>-0.0584</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5533</v>
+        <v>0.6338</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.7006</v>
+        <v>0.7527</v>
       </c>
     </row>
     <row r="9">
@@ -802,28 +802,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6847</v>
+        <v>0.7219</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1012</v>
+        <v>-0.0815</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1011</v>
+        <v>0.0858</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0722</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0358</v>
+        <v>0.0432</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0461</v>
+        <v>-0.0563</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0129</v>
+        <v>-0.0166</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4981</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.6847</v>
+        <v>0.7219</v>
       </c>
     </row>
     <row r="10">
@@ -846,28 +846,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8078</v>
+        <v>0.806</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.0346</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0663</v>
+        <v>-0.0747</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0386</v>
+        <v>-0.0994</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01</v>
+        <v>0.0071</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0825</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0601</v>
+        <v>-0.0341</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6791</v>
+        <v>0.6743</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.8078</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="11">
@@ -890,28 +890,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6884</v>
+        <v>0.7076</v>
       </c>
       <c r="C11" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0291</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1339</v>
+        <v>-0.1177</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0091</v>
+        <v>0.0179</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1395</v>
+        <v>-0.1165</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1314</v>
+        <v>0.1029</v>
       </c>
       <c r="H11" t="n">
-        <v>0.113</v>
+        <v>0.0927</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5414</v>
+        <v>0.5484</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.6884</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="12">
@@ -934,28 +934,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1759</v>
+        <v>0.1796</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6294</v>
+        <v>0.1312</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0204</v>
+        <v>0.026</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1213</v>
+        <v>0.6268</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0076</v>
+        <v>-0.0196</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2306</v>
+        <v>-0.2095</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0345</v>
+        <v>0.0432</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4967</v>
+        <v>0.4892</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -964,11 +964,11 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.6294</v>
+        <v>0.6268</v>
       </c>
     </row>
     <row r="13">
@@ -978,28 +978,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.0039</v>
+        <v>-0.0462</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6545</v>
+        <v>0.093</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0361</v>
+        <v>0.0199</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0707</v>
+        <v>0.6889</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0154</v>
+        <v>-0.0289</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01</v>
+        <v>0.0078</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0242</v>
+        <v>0.0481</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4355</v>
+        <v>0.489</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1008,11 +1008,11 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.6545</v>
+        <v>0.6889</v>
       </c>
     </row>
     <row r="14">
@@ -1022,28 +1022,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.0619</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6746</v>
+        <v>-0.0159</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.075</v>
+        <v>-0.0828</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0138</v>
+        <v>0.6616</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0314</v>
+        <v>0.0414</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0901</v>
+        <v>0.1239</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0183</v>
+        <v>-0.0395</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4768</v>
+        <v>0.4673</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1052,11 +1052,11 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.6746</v>
+        <v>0.6616</v>
       </c>
     </row>
     <row r="15">
@@ -1066,28 +1066,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0219</v>
+        <v>0.0293</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7563</v>
+        <v>-0.129</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0583</v>
+        <v>0.0582</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.11</v>
+        <v>0.7875</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0374</v>
+        <v>-0.025</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1152</v>
+        <v>0.1171</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0696</v>
+        <v>-0.0828</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.6622</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1096,11 +1096,11 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.7563</v>
+        <v>0.7875</v>
       </c>
     </row>
     <row r="16">
@@ -1110,28 +1110,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0182</v>
+        <v>0.0328</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6993</v>
+        <v>-0.0059</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0622</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0404</v>
+        <v>0.6673</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0844</v>
+        <v>0.0935</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0979</v>
+        <v>-0.1328</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0629</v>
+        <v>0.1019</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5155</v>
+        <v>0.4902</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1140,11 +1140,11 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.6993</v>
+        <v>0.6673</v>
       </c>
     </row>
     <row r="17">
@@ -1154,28 +1154,28 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.0336</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.0181</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.0158</v>
       </c>
-      <c r="C17" t="n">
-        <v>0.0929</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-0.06809999999999999</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.0391</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-0.0292</v>
-      </c>
       <c r="H17" t="n">
-        <v>0.6213</v>
+        <v>0.5646</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4207</v>
+        <v>0.3571</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.6213</v>
+        <v>0.5646</v>
       </c>
     </row>
     <row r="18">
@@ -1198,28 +1198,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1229</v>
+        <v>-0.1688</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2462</v>
+        <v>-0.0723</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0475</v>
+        <v>-0.0728</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.2714</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1252</v>
+        <v>-0.1174</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0993</v>
+        <v>0.0688</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7212</v>
+        <v>0.7922</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6288</v>
+        <v>0.7589</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.7212</v>
+        <v>0.7922</v>
       </c>
     </row>
     <row r="19">
@@ -1242,28 +1242,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.1132</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.2254</v>
+        <v>0.0374</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1186</v>
+        <v>0.1299</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0311</v>
+        <v>-0.2014</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0221</v>
+        <v>-0.0437</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0554</v>
+        <v>0.0882</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.5249</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4048</v>
+        <v>0.3568</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.5249</v>
       </c>
     </row>
     <row r="20">
@@ -1286,28 +1286,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.003</v>
+        <v>-0.0083</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0067</v>
+        <v>-0.1513</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0449</v>
+        <v>0.0003</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1153</v>
+        <v>-0.0346</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0286</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1293</v>
+        <v>0.1625</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4901</v>
+        <v>0.476</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2731</v>
+        <v>0.2827</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.4901</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="21">
@@ -1330,28 +1330,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0318</v>
+        <v>0.017</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0343</v>
+        <v>-0.0201</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0242</v>
+        <v>-0.0579</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0857</v>
+        <v>0.083</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.1248</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7369</v>
+        <v>0.7802</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.6353</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.7369</v>
+        <v>0.7802</v>
       </c>
     </row>
     <row r="22">
@@ -1374,28 +1374,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.095</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0384</v>
+        <v>0.7117</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6744</v>
+        <v>0.0551</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0153</v>
+        <v>-0.0164</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1232</v>
+        <v>0.1261</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.067</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4894</v>
+        <v>0.5441</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1404,11 +1404,11 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.6744</v>
+        <v>0.7117</v>
       </c>
     </row>
     <row r="23">
@@ -1418,28 +1418,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0322</v>
+        <v>-0.0294</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0196</v>
+        <v>0.8359</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0538</v>
+        <v>0.0492</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7948</v>
+        <v>-0.0153</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0242</v>
+        <v>0.0201</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0822</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0323</v>
+        <v>0.0259</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6445</v>
+        <v>0.7104</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1448,11 +1448,11 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.7948</v>
+        <v>0.8359</v>
       </c>
     </row>
     <row r="24">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0161</v>
+        <v>0.0175</v>
       </c>
       <c r="C24" t="n">
-        <v>0.055</v>
+        <v>0.5742</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0564</v>
+        <v>-0.0623</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5433</v>
+        <v>0.0034</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1449</v>
+        <v>-0.0866</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0989</v>
+        <v>0.1009</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0062</v>
+        <v>-0.0263</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3324</v>
+        <v>0.3523</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1492,11 +1492,11 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.5433</v>
+        <v>0.5742</v>
       </c>
     </row>
     <row r="25">
@@ -1506,28 +1506,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0291</v>
+        <v>0.0174</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0357</v>
+        <v>0.0347</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6884</v>
+        <v>-0.0512</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0806</v>
+        <v>0.0776</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0031</v>
+        <v>-0.019</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0257</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4897</v>
+        <v>0.5381</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1536,11 +1536,11 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.6884</v>
+        <v>0.7262999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0572</v>
+        <v>0.0488</v>
       </c>
       <c r="C26" t="n">
-        <v>0.003</v>
+        <v>0.6831</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0453</v>
+        <v>-0.0346</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6579</v>
+        <v>0.0137</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1012</v>
+        <v>0.1066</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0451</v>
+        <v>-0.0355</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0126</v>
+        <v>-0.0225</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4506</v>
+        <v>0.4835</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1580,11 +1580,11 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.6579</v>
+        <v>0.6831</v>
       </c>
     </row>
     <row r="27">
@@ -1594,28 +1594,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0605</v>
+        <v>-0.0477</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0322</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0574</v>
+        <v>-0.061</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0607</v>
+        <v>0.0496</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0832</v>
+        <v>0.0915</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0195</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5495</v>
+        <v>0.6113</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.7645999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1638,28 +1638,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1321</v>
+        <v>-0.1418</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0538</v>
+        <v>0.033</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0115</v>
+        <v>0.02</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0227</v>
+        <v>-0.0607</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6764</v>
+        <v>0.7339</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1132</v>
+        <v>0.0886</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0367</v>
+        <v>0.0366</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4927</v>
+        <v>0.573</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.6764</v>
+        <v>0.7339</v>
       </c>
     </row>
     <row r="29">
@@ -1682,28 +1682,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0139</v>
+        <v>0.0083</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1118</v>
+        <v>0.0508</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.081</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0142</v>
+        <v>0.1042</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6286</v>
+        <v>0.6523</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1697</v>
+        <v>0.1189</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0968</v>
+        <v>-0.0456</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4527</v>
+        <v>0.4618</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.6286</v>
+        <v>0.6523</v>
       </c>
     </row>
     <row r="30">
@@ -1726,28 +1726,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1189</v>
+        <v>0.1166</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0146</v>
+        <v>0.0182</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1083</v>
+        <v>0.0902</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0139</v>
+        <v>-0.0434</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6748</v>
+        <v>0.6715</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.148</v>
+        <v>-0.1247</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0172</v>
+        <v>-0.0073</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5038</v>
+        <v>0.4905</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.6748</v>
+        <v>0.6715</v>
       </c>
     </row>
     <row r="31">
@@ -1770,28 +1770,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.051</v>
+        <v>0.0451</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0055</v>
+        <v>0.0408</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.041</v>
+        <v>-0.0204</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0391</v>
+        <v>0.0206</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6291</v>
+        <v>0.6365</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0915</v>
+        <v>-0.0973</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1148</v>
+        <v>0.1225</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4232</v>
+        <v>0.4342</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.6291</v>
+        <v>0.6365</v>
       </c>
     </row>
     <row r="32">
@@ -1814,28 +1814,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0828</v>
+        <v>0.0843</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0672</v>
+        <v>-0.1024</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7085</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0906</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.076</v>
+        <v>-0.0505</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0537</v>
+        <v>-0.0675</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0463</v>
+        <v>0.0356</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5323</v>
+        <v>0.5616</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0.7085</v>
+        <v>0.7272999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1858,28 +1858,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0542</v>
+        <v>-0.052</v>
       </c>
       <c r="C33" t="n">
-        <v>0.028</v>
+        <v>0.0576</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6403</v>
+        <v>0.6798</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0354</v>
+        <v>-0.0129</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0601</v>
+        <v>0.0673</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.1188</v>
+        <v>-0.1053</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0584</v>
+        <v>0.0518</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4362</v>
+        <v>0.4867</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.6403</v>
+        <v>0.6798</v>
       </c>
     </row>
     <row r="34">
@@ -1902,28 +1902,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0023</v>
+        <v>-0.0123</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1386</v>
+        <v>0.0294</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7923</v>
+        <v>0.843</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0493</v>
+        <v>-0.1224</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0184</v>
+        <v>-0.0042</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0717</v>
+        <v>0.0883</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.0362</v>
+        <v>-0.0504</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6562</v>
+        <v>0.737</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.7923</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="35">
@@ -1946,28 +1946,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.0283</v>
+        <v>-0.0452</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0136</v>
+        <v>0.0363</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7054</v>
+        <v>0.7258</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0522</v>
+        <v>0.0146</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1028</v>
+        <v>-0.0867</v>
       </c>
       <c r="G35" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.0434</v>
+        <v>-0.0324</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5233</v>
+        <v>0.5467</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.7054</v>
+        <v>0.7258</v>
       </c>
     </row>
     <row r="36">
@@ -1990,28 +1990,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.0624</v>
+        <v>-0.0413</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1454</v>
+        <v>-0.0058</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5648</v>
+        <v>0.595</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.0055</v>
+        <v>0.1374</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0438</v>
+        <v>0.036</v>
       </c>
       <c r="G36" t="n">
-        <v>0.109</v>
+        <v>0.1048</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.0224</v>
+        <v>-0.0407</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3584</v>
+        <v>0.3886</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.5648</v>
+        <v>0.595</v>
       </c>
     </row>
   </sheetData>
@@ -2070,13 +2070,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.8128</v>
+        <v>3.0361</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0804</v>
+        <v>0.0867</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0804</v>
+        <v>0.0867</v>
       </c>
     </row>
     <row r="3">
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.5847</v>
+        <v>2.7252</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0738</v>
+        <v>0.0779</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1542</v>
+        <v>0.1646</v>
       </c>
     </row>
     <row r="4">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.4884</v>
+        <v>2.6975</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0711</v>
+        <v>0.0771</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2253</v>
+        <v>0.2417</v>
       </c>
     </row>
     <row r="5">
@@ -2118,13 +2118,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.4396</v>
+        <v>2.5935</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0697</v>
+        <v>0.0741</v>
       </c>
       <c r="D5" t="n">
-        <v>0.295</v>
+        <v>0.3158</v>
       </c>
     </row>
     <row r="6">
@@ -2134,13 +2134,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.4021</v>
+        <v>2.5523</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3636</v>
+        <v>0.3887</v>
       </c>
     </row>
     <row r="7">
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.2765</v>
+        <v>2.3644</v>
       </c>
       <c r="C7" t="n">
-        <v>0.065</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4287</v>
+        <v>0.4563</v>
       </c>
     </row>
     <row r="8">
@@ -2166,13 +2166,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.101</v>
+        <v>2.1504</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06</v>
+        <v>0.0614</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4887</v>
+        <v>0.5177</v>
       </c>
     </row>
   </sheetData>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8952069122294213</v>
+        <v>0.9147423882583382</v>
       </c>
     </row>
     <row r="3">
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8976865796726642</v>
+        <v>0.9170492951633935</v>
       </c>
     </row>
     <row r="4">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8814188040516471</v>
+        <v>0.9014966404000418</v>
       </c>
     </row>
     <row r="5">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8919049158404605</v>
+        <v>0.9007892242314909</v>
       </c>
     </row>
     <row r="6">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9047890539238137</v>
+        <v>0.9248676245549348</v>
       </c>
     </row>
     <row r="7">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8648157811999649</v>
+        <v>0.8977668182777834</v>
       </c>
     </row>
     <row r="8">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8620172850182062</v>
+        <v>0.8815049506006055</v>
       </c>
     </row>
     <row r="9">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8926817328952232</v>
+        <v>0.9175278264257442</v>
       </c>
     </row>
     <row r="10">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8767321413066468</v>
+        <v>0.8996110285484289</v>
       </c>
     </row>
     <row r="11">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8566315733642541</v>
+        <v>0.8880294095747662</v>
       </c>
     </row>
     <row r="12">
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8477494948942793</v>
+        <v>0.8698216210377718</v>
       </c>
     </row>
     <row r="13">
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8967024735580937</v>
+        <v>0.9043625633132409</v>
       </c>
     </row>
     <row r="14">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8569057725885321</v>
+        <v>0.8724652422754391</v>
       </c>
     </row>
     <row r="15">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.879197037450675</v>
+        <v>0.8863638944258089</v>
       </c>
     </row>
     <row r="16">
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8618261080661549</v>
+        <v>0.8975578977956475</v>
       </c>
     </row>
     <row r="17">
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9173874953338493</v>
+        <v>0.9332929968735453</v>
       </c>
     </row>
     <row r="18">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8425372644942555</v>
+        <v>0.8334082363156421</v>
       </c>
     </row>
     <row r="19">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7867347113557328</v>
+        <v>0.8295417798556746</v>
       </c>
     </row>
     <row r="20">
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8900995197213254</v>
+        <v>0.8676294261272743</v>
       </c>
     </row>
     <row r="21">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8149811850302677</v>
+        <v>0.8438448806068808</v>
       </c>
     </row>
     <row r="22">
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8572159068117174</v>
+        <v>0.8929715419607965</v>
       </c>
     </row>
     <row r="23">
@@ -2418,7 +2418,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8259181088184874</v>
+        <v>0.8716835665024401</v>
       </c>
     </row>
     <row r="24">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7780791556758376</v>
+        <v>0.8153458019404214</v>
       </c>
     </row>
     <row r="25">
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8587069813319211</v>
+        <v>0.8915361580677684</v>
       </c>
     </row>
     <row r="26">
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8492235510503405</v>
+        <v>0.8952776465594364</v>
       </c>
     </row>
     <row r="27">
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8102126168280923</v>
+        <v>0.8259774796388895</v>
       </c>
     </row>
     <row r="28">
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8152420591888436</v>
+        <v>0.8477605842145112</v>
       </c>
     </row>
     <row r="29">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8344307939833321</v>
+        <v>0.8667086089368635</v>
       </c>
     </row>
     <row r="30">
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8517438074295793</v>
+        <v>0.8593406629991561</v>
       </c>
     </row>
     <row r="31">
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8668603175850017</v>
+        <v>0.8881891575977632</v>
       </c>
     </row>
     <row r="32">
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8550169686203348</v>
+        <v>0.8827685822998389</v>
       </c>
     </row>
     <row r="33">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8331776621708789</v>
+        <v>0.8708600126815285</v>
       </c>
     </row>
     <row r="34">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8564078308002707</v>
+        <v>0.8747411586561045</v>
       </c>
     </row>
     <row r="35">
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8275505186982263</v>
+        <v>0.8505976790804988</v>
       </c>
     </row>
     <row r="36">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9151650874086861</v>
+        <v>0.9255971483242029</v>
       </c>
     </row>
   </sheetData>
